--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103074</v>
+        <v>103077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 146-2024 artfynd.xlsx
+++ b/artfynd/S 146-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136092112</v>
       </c>
       <c r="B3" t="n">
-        <v>103077</v>
+        <v>103078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
